--- a/output/pdf_financials_xlsx/SCMI.xlsx
+++ b/output/pdf_financials_xlsx/SCMI.xlsx
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.022725</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.271243</v>
       </c>
     </row>
     <row r="93">
@@ -2722,7 +2722,11 @@
           <t>Reserves 4, 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.022725</v>
       </c>

--- a/output/pdf_financials_xlsx/SCMI.xlsx
+++ b/output/pdf_financials_xlsx/SCMI.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005553</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.366328</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.739619</v>
+        <v>-0.7451719999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-26.017206</v>
+        <v>-26.383534</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.739619</v>
+        <v>-0.7451719999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-25.746544</v>
+        <v>-26.112872</v>
       </c>
     </row>
     <row r="30">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">

--- a/output/pdf_financials_xlsx/SCMI.xlsx
+++ b/output/pdf_financials_xlsx/SCMI.xlsx
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.39669</v>
       </c>
     </row>
     <row r="112">
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.39669</v>
       </c>
     </row>
     <row r="135">
@@ -2211,7 +2211,7 @@
         <v>-0.805518</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-22.159182</v>
+        <v>-22.555872</v>
       </c>
     </row>
   </sheetData>
@@ -3156,7 +3156,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
